--- a/KIHON.xlsx
+++ b/KIHON.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\logistic_regression_with_r_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/baba/github.noindex/logistic_regression_with_r_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56665739-7688-4736-9C23-EB91CD900149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FA5AE22-A3BC-6148-A317-8DACDEA89A53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19605" yWindow="705" windowWidth="13200" windowHeight="14025" tabRatio="860" xr2:uid="{C26B4007-F44F-47A4-8077-EAEB4996189A}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" tabRatio="860" xr2:uid="{C26B4007-F44F-47A4-8077-EAEB4996189A}"/>
   </bookViews>
   <sheets>
     <sheet name="仮説データ" sheetId="7" r:id="rId1"/>
@@ -60,10 +60,6 @@
   </si>
   <si>
     <t>ある</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>年齢　</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -153,12 +149,16 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>年齢</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -558,41 +558,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EE74A6F-08AC-4C40-A211-2F9768E89CE4}">
   <dimension ref="A1:J120"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="18"/>
   <sheetData>
-    <row r="1" spans="1:10" ht="33.75" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" ht="36">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="G1" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>1</v>
       </c>
@@ -609,7 +609,7 @@
         <v>57</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>20</v>
@@ -618,13 +618,13 @@
         <v>2</v>
       </c>
       <c r="I2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3">
         <v>2</v>
       </c>
@@ -641,7 +641,7 @@
         <v>31</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>9</v>
@@ -650,13 +650,13 @@
         <v>2</v>
       </c>
       <c r="I3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>4</v>
       </c>
@@ -673,7 +673,7 @@
         <v>42</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>18</v>
@@ -682,18 +682,18 @@
         <v>2</v>
       </c>
       <c r="I4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
         <v>2</v>
@@ -705,7 +705,7 @@
         <v>57</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -714,18 +714,18 @@
         <v>2</v>
       </c>
       <c r="I5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
         <v>2</v>
@@ -737,7 +737,7 @@
         <v>34</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>12</v>
@@ -746,13 +746,13 @@
         <v>2</v>
       </c>
       <c r="I6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>7</v>
       </c>
@@ -769,27 +769,27 @@
         <v>31</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>12</v>
       </c>
       <c r="H7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s">
         <v>1</v>
@@ -801,7 +801,7 @@
         <v>46</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -810,18 +810,18 @@
         <v>2</v>
       </c>
       <c r="I8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" t="s">
         <v>1</v>
@@ -833,27 +833,27 @@
         <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>29</v>
       </c>
       <c r="H9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" t="s">
         <v>2</v>
@@ -865,7 +865,7 @@
         <v>70</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G10">
         <v>12</v>
@@ -874,13 +874,13 @@
         <v>2</v>
       </c>
       <c r="I10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>11</v>
       </c>
@@ -897,7 +897,7 @@
         <v>20</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11">
         <v>12</v>
@@ -906,13 +906,13 @@
         <v>2</v>
       </c>
       <c r="I11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12">
         <v>12</v>
       </c>
@@ -929,27 +929,27 @@
         <v>34</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G12">
         <v>36</v>
       </c>
       <c r="H12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13">
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="s">
         <v>1</v>
@@ -961,7 +961,7 @@
         <v>55</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -970,13 +970,13 @@
         <v>2</v>
       </c>
       <c r="I13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14">
         <v>14</v>
       </c>
@@ -993,22 +993,22 @@
         <v>28</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G14">
         <v>18</v>
       </c>
       <c r="H14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15">
         <v>15</v>
       </c>
@@ -1025,7 +1025,7 @@
         <v>60</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G15">
         <v>6</v>
@@ -1034,13 +1034,13 @@
         <v>2</v>
       </c>
       <c r="I15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16">
         <v>16</v>
       </c>
@@ -1057,27 +1057,27 @@
         <v>20</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G16">
         <v>12</v>
       </c>
       <c r="H16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17">
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C17" t="s">
         <v>2</v>
@@ -1089,7 +1089,7 @@
         <v>47</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G17">
         <v>74</v>
@@ -1098,13 +1098,13 @@
         <v>2</v>
       </c>
       <c r="I17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18">
         <v>20</v>
       </c>
@@ -1121,27 +1121,27 @@
         <v>23</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G18">
         <v>37</v>
       </c>
       <c r="H18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J18" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19">
         <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C19" t="s">
         <v>2</v>
@@ -1153,7 +1153,7 @@
         <v>26</v>
       </c>
       <c r="F19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G19">
         <v>14</v>
@@ -1162,18 +1162,18 @@
         <v>2</v>
       </c>
       <c r="I19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20">
         <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C20" t="s">
         <v>2</v>
@@ -1185,7 +1185,7 @@
         <v>68</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G20">
         <v>10</v>
@@ -1194,18 +1194,18 @@
         <v>2</v>
       </c>
       <c r="I20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J20" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21">
         <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C21" t="s">
         <v>1</v>
@@ -1217,27 +1217,27 @@
         <v>49</v>
       </c>
       <c r="F21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G21">
         <v>36</v>
       </c>
       <c r="H21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J21" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22">
         <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C22" t="s">
         <v>2</v>
@@ -1249,7 +1249,7 @@
         <v>31</v>
       </c>
       <c r="F22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G22">
         <v>11</v>
@@ -1258,13 +1258,13 @@
         <v>2</v>
       </c>
       <c r="I22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J22" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23">
         <v>26</v>
       </c>
@@ -1281,7 +1281,7 @@
         <v>30</v>
       </c>
       <c r="F23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G23">
         <v>27</v>
@@ -1290,18 +1290,18 @@
         <v>2</v>
       </c>
       <c r="I23" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J23" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24">
         <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C24" t="s">
         <v>1</v>
@@ -1313,7 +1313,7 @@
         <v>58</v>
       </c>
       <c r="F24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G24">
         <v>3</v>
@@ -1322,13 +1322,13 @@
         <v>2</v>
       </c>
       <c r="I24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J24" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25">
         <v>28</v>
       </c>
@@ -1345,7 +1345,7 @@
         <v>39</v>
       </c>
       <c r="F25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G25">
         <v>48</v>
@@ -1354,13 +1354,13 @@
         <v>2</v>
       </c>
       <c r="I25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J25" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26">
         <v>29</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>58</v>
       </c>
       <c r="F26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G26">
         <v>48</v>
@@ -1386,18 +1386,18 @@
         <v>2</v>
       </c>
       <c r="I26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J26" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27">
         <v>30</v>
       </c>
       <c r="B27" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C27" t="s">
         <v>2</v>
@@ -1409,7 +1409,7 @@
         <v>26</v>
       </c>
       <c r="F27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G27">
         <v>10</v>
@@ -1418,13 +1418,13 @@
         <v>2</v>
       </c>
       <c r="I27" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J27" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28">
         <v>31</v>
       </c>
@@ -1441,22 +1441,22 @@
         <v>46</v>
       </c>
       <c r="F28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G28">
         <v>37</v>
       </c>
       <c r="H28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J28" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29">
         <v>32</v>
       </c>
@@ -1473,22 +1473,22 @@
         <v>40</v>
       </c>
       <c r="F29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G29">
         <v>29</v>
       </c>
       <c r="H29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30">
         <v>34</v>
       </c>
@@ -1505,7 +1505,7 @@
         <v>43</v>
       </c>
       <c r="F30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G30">
         <v>23</v>
@@ -1514,13 +1514,13 @@
         <v>2</v>
       </c>
       <c r="I30" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J30" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31">
         <v>35</v>
       </c>
@@ -1537,7 +1537,7 @@
         <v>48</v>
       </c>
       <c r="F31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G31">
         <v>36</v>
@@ -1546,18 +1546,18 @@
         <v>2</v>
       </c>
       <c r="I31" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J31" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32">
         <v>36</v>
       </c>
       <c r="B32" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C32" t="s">
         <v>1</v>
@@ -1569,27 +1569,27 @@
         <v>20</v>
       </c>
       <c r="F32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G32">
         <v>24</v>
       </c>
       <c r="H32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J32" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33">
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C33" t="s">
         <v>2</v>
@@ -1601,27 +1601,27 @@
         <v>22</v>
       </c>
       <c r="F33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G33">
         <v>36</v>
       </c>
       <c r="H33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I33" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J33" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34">
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C34" t="s">
         <v>1</v>
@@ -1633,27 +1633,27 @@
         <v>59</v>
       </c>
       <c r="F34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G34">
         <v>3</v>
       </c>
       <c r="H34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J34" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35">
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C35" t="s">
         <v>1</v>
@@ -1665,7 +1665,7 @@
         <v>37</v>
       </c>
       <c r="F35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G35">
         <v>5</v>
@@ -1674,13 +1674,13 @@
         <v>2</v>
       </c>
       <c r="I35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J35" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36">
         <v>42</v>
       </c>
@@ -1697,7 +1697,7 @@
         <v>41</v>
       </c>
       <c r="F36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G36">
         <v>24</v>
@@ -1706,18 +1706,18 @@
         <v>2</v>
       </c>
       <c r="I36" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37">
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C37" t="s">
         <v>1</v>
@@ -1729,7 +1729,7 @@
         <v>32</v>
       </c>
       <c r="F37" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G37">
         <v>31</v>
@@ -1738,18 +1738,18 @@
         <v>2</v>
       </c>
       <c r="I37" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J37" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38">
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C38" t="s">
         <v>1</v>
@@ -1761,7 +1761,7 @@
         <v>36</v>
       </c>
       <c r="F38" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G38">
         <v>4</v>
@@ -1770,18 +1770,18 @@
         <v>2</v>
       </c>
       <c r="I38" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J38" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39">
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C39" t="s">
         <v>1</v>
@@ -1793,7 +1793,7 @@
         <v>42</v>
       </c>
       <c r="F39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G39">
         <v>13</v>
@@ -1802,13 +1802,13 @@
         <v>2</v>
       </c>
       <c r="I39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J39" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40">
         <v>46</v>
       </c>
@@ -1825,7 +1825,7 @@
         <v>43</v>
       </c>
       <c r="F40" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G40">
         <v>27</v>
@@ -1834,18 +1834,18 @@
         <v>2</v>
       </c>
       <c r="I40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J40" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41">
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C41" t="s">
         <v>1</v>
@@ -1857,7 +1857,7 @@
         <v>61</v>
       </c>
       <c r="F41" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G41">
         <v>36</v>
@@ -1866,18 +1866,18 @@
         <v>2</v>
       </c>
       <c r="I41" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J41" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42">
         <v>49</v>
       </c>
       <c r="B42" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C42" t="s">
         <v>2</v>
@@ -1889,7 +1889,7 @@
         <v>31</v>
       </c>
       <c r="F42" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G42">
         <v>12</v>
@@ -1898,13 +1898,13 @@
         <v>2</v>
       </c>
       <c r="I42" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J42" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43">
         <v>50</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>56</v>
       </c>
       <c r="F43" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G43">
         <v>14</v>
@@ -1930,18 +1930,18 @@
         <v>2</v>
       </c>
       <c r="I43" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J43" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
       <c r="A44">
         <v>51</v>
       </c>
       <c r="B44" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C44" t="s">
         <v>1</v>
@@ -1953,7 +1953,7 @@
         <v>46</v>
       </c>
       <c r="F44" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G44">
         <v>12</v>
@@ -1962,18 +1962,18 @@
         <v>2</v>
       </c>
       <c r="I44" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J44" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
       <c r="A45">
         <v>52</v>
       </c>
       <c r="B45" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C45" t="s">
         <v>1</v>
@@ -1985,7 +1985,7 @@
         <v>39</v>
       </c>
       <c r="F45" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G45">
         <v>36</v>
@@ -1994,18 +1994,18 @@
         <v>2</v>
       </c>
       <c r="I45" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J45" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
       <c r="A46">
         <v>53</v>
       </c>
       <c r="B46" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C46" t="s">
         <v>2</v>
@@ -2017,7 +2017,7 @@
         <v>57</v>
       </c>
       <c r="F46" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G46">
         <v>16</v>
@@ -2026,18 +2026,18 @@
         <v>2</v>
       </c>
       <c r="I46" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J46" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
       <c r="A47">
         <v>54</v>
       </c>
       <c r="B47" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C47" t="s">
         <v>2</v>
@@ -2049,7 +2049,7 @@
         <v>62</v>
       </c>
       <c r="F47" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G47">
         <v>16</v>
@@ -2058,13 +2058,13 @@
         <v>2</v>
       </c>
       <c r="I47" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J47" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
       <c r="A48">
         <v>55</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>43</v>
       </c>
       <c r="F48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G48">
         <v>28</v>
@@ -2090,13 +2090,13 @@
         <v>2</v>
       </c>
       <c r="I48" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J48" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
       <c r="A49">
         <v>56</v>
       </c>
@@ -2113,7 +2113,7 @@
         <v>32</v>
       </c>
       <c r="F49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G49">
         <v>6</v>
@@ -2122,13 +2122,13 @@
         <v>2</v>
       </c>
       <c r="I49" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J49" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
       <c r="A50">
         <v>57</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>46</v>
       </c>
       <c r="F50" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -2154,13 +2154,13 @@
         <v>2</v>
       </c>
       <c r="I50" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J50" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
       <c r="A51">
         <v>58</v>
       </c>
@@ -2177,22 +2177,22 @@
         <v>22</v>
       </c>
       <c r="F51" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G51">
         <v>25</v>
       </c>
       <c r="H51" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I51" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J51" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
       <c r="A52">
         <v>59</v>
       </c>
@@ -2209,7 +2209,7 @@
         <v>37</v>
       </c>
       <c r="F52" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G52">
         <v>10</v>
@@ -2218,18 +2218,18 @@
         <v>2</v>
       </c>
       <c r="I52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J52" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
       <c r="A53">
         <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C53" t="s">
         <v>2</v>
@@ -2241,7 +2241,7 @@
         <v>29</v>
       </c>
       <c r="F53" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G53">
         <v>25</v>
@@ -2250,13 +2250,13 @@
         <v>2</v>
       </c>
       <c r="I53" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J53" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
       <c r="A54">
         <v>61</v>
       </c>
@@ -2273,7 +2273,7 @@
         <v>36</v>
       </c>
       <c r="F54" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G54">
         <v>14</v>
@@ -2282,13 +2282,13 @@
         <v>2</v>
       </c>
       <c r="I54" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J54" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
       <c r="A55">
         <v>62</v>
       </c>
@@ -2305,22 +2305,22 @@
         <v>41</v>
       </c>
       <c r="F55" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G55">
         <v>12</v>
       </c>
       <c r="H55" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I55" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J55" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
       <c r="A56">
         <v>63</v>
       </c>
@@ -2337,7 +2337,7 @@
         <v>63</v>
       </c>
       <c r="F56" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G56">
         <v>32</v>
@@ -2346,18 +2346,18 @@
         <v>2</v>
       </c>
       <c r="I56" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J56" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
       <c r="A57">
         <v>64</v>
       </c>
       <c r="B57" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C57" t="s">
         <v>1</v>
@@ -2369,7 +2369,7 @@
         <v>39</v>
       </c>
       <c r="F57" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G57">
         <v>6</v>
@@ -2378,18 +2378,18 @@
         <v>2</v>
       </c>
       <c r="I57" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J57" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
       <c r="A58">
         <v>66</v>
       </c>
       <c r="B58" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C58" t="s">
         <v>2</v>
@@ -2401,7 +2401,7 @@
         <v>35</v>
       </c>
       <c r="F58" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G58">
         <v>29</v>
@@ -2410,18 +2410,18 @@
         <v>2</v>
       </c>
       <c r="I58" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J58" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
       <c r="A59">
         <v>67</v>
       </c>
       <c r="B59" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C59" t="s">
         <v>1</v>
@@ -2433,22 +2433,22 @@
         <v>30</v>
       </c>
       <c r="F59" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G59">
         <v>15</v>
       </c>
       <c r="H59" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I59" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J59" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
       <c r="A60">
         <v>68</v>
       </c>
@@ -2465,7 +2465,7 @@
         <v>49</v>
       </c>
       <c r="F60" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G60">
         <v>3</v>
@@ -2474,13 +2474,13 @@
         <v>2</v>
       </c>
       <c r="I60" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J60" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
       <c r="A61">
         <v>69</v>
       </c>
@@ -2497,7 +2497,7 @@
         <v>35</v>
       </c>
       <c r="F61" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G61">
         <v>25</v>
@@ -2506,18 +2506,18 @@
         <v>2</v>
       </c>
       <c r="I61" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J61" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
       <c r="A62">
         <v>70</v>
       </c>
       <c r="B62" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C62" t="s">
         <v>1</v>
@@ -2529,7 +2529,7 @@
         <v>41</v>
       </c>
       <c r="F62" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G62">
         <v>22</v>
@@ -2538,13 +2538,13 @@
         <v>2</v>
       </c>
       <c r="I62" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J62" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
       <c r="A63">
         <v>71</v>
       </c>
@@ -2561,7 +2561,7 @@
         <v>35</v>
       </c>
       <c r="F63" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G63">
         <v>31</v>
@@ -2570,18 +2570,18 @@
         <v>2</v>
       </c>
       <c r="I63" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J63" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
       <c r="A64">
         <v>72</v>
       </c>
       <c r="B64" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C64" t="s">
         <v>2</v>
@@ -2593,7 +2593,7 @@
         <v>19</v>
       </c>
       <c r="F64" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G64">
         <v>13</v>
@@ -2602,13 +2602,13 @@
         <v>2</v>
       </c>
       <c r="I64" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J64" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
       <c r="A65">
         <v>73</v>
       </c>
@@ -2625,7 +2625,7 @@
         <v>37</v>
       </c>
       <c r="F65" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G65">
         <v>9</v>
@@ -2634,13 +2634,13 @@
         <v>2</v>
       </c>
       <c r="I65" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J65" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
       <c r="A66">
         <v>74</v>
       </c>
@@ -2657,27 +2657,27 @@
         <v>50</v>
       </c>
       <c r="F66" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G66">
         <v>16</v>
       </c>
       <c r="H66" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I66" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J66" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
       <c r="A67">
         <v>75</v>
       </c>
       <c r="B67" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C67" t="s">
         <v>1</v>
@@ -2689,7 +2689,7 @@
         <v>31</v>
       </c>
       <c r="F67" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G67">
         <v>11</v>
@@ -2698,13 +2698,13 @@
         <v>2</v>
       </c>
       <c r="I67" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J67" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
       <c r="A68">
         <v>76</v>
       </c>
@@ -2721,7 +2721,7 @@
         <v>33</v>
       </c>
       <c r="F68" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G68">
         <v>3</v>
@@ -2730,18 +2730,18 @@
         <v>2</v>
       </c>
       <c r="I68" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J68" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
       <c r="A69">
         <v>77</v>
       </c>
       <c r="B69" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C69" t="s">
         <v>1</v>
@@ -2753,7 +2753,7 @@
         <v>34</v>
       </c>
       <c r="F69" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G69">
         <v>3</v>
@@ -2762,13 +2762,13 @@
         <v>2</v>
       </c>
       <c r="I69" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J69" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
       <c r="A70">
         <v>78</v>
       </c>
@@ -2785,7 +2785,7 @@
         <v>40</v>
       </c>
       <c r="F70" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G70">
         <v>3</v>
@@ -2794,13 +2794,13 @@
         <v>2</v>
       </c>
       <c r="I70" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J70" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
       <c r="A71">
         <v>79</v>
       </c>
@@ -2817,27 +2817,27 @@
         <v>40</v>
       </c>
       <c r="F71" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G71">
         <v>12</v>
       </c>
       <c r="H71" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I71" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J71" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
       <c r="A72">
         <v>80</v>
       </c>
       <c r="B72" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C72" t="s">
         <v>1</v>
@@ -2849,27 +2849,27 @@
         <v>32</v>
       </c>
       <c r="F72" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G72">
         <v>7</v>
       </c>
       <c r="H72" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I72" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J72" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
       <c r="A73">
         <v>81</v>
       </c>
       <c r="B73" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C73" t="s">
         <v>1</v>
@@ -2881,22 +2881,22 @@
         <v>21</v>
       </c>
       <c r="F73" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G73">
         <v>13</v>
       </c>
       <c r="H73" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I73" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J73" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
       <c r="A74">
         <v>82</v>
       </c>
@@ -2913,7 +2913,7 @@
         <v>20</v>
       </c>
       <c r="F74" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G74">
         <v>16</v>
@@ -2922,18 +2922,18 @@
         <v>2</v>
       </c>
       <c r="I74" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J74" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10">
       <c r="A75">
         <v>84</v>
       </c>
       <c r="B75" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C75" t="s">
         <v>1</v>
@@ -2945,7 +2945,7 @@
         <v>31</v>
       </c>
       <c r="F75" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G75">
         <v>16</v>
@@ -2954,18 +2954,18 @@
         <v>2</v>
       </c>
       <c r="I75" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J75" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10">
       <c r="A76">
         <v>85</v>
       </c>
       <c r="B76" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C76" t="s">
         <v>1</v>
@@ -2977,22 +2977,22 @@
         <v>33</v>
       </c>
       <c r="F76" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G76">
         <v>9</v>
       </c>
       <c r="H76" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I76" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J76" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10">
       <c r="A77">
         <v>86</v>
       </c>
@@ -3009,7 +3009,7 @@
         <v>32</v>
       </c>
       <c r="F77" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G77">
         <v>13</v>
@@ -3018,18 +3018,18 @@
         <v>2</v>
       </c>
       <c r="I77" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J77" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10">
       <c r="A78">
         <v>87</v>
       </c>
       <c r="B78" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C78" t="s">
         <v>2</v>
@@ -3041,7 +3041,7 @@
         <v>21</v>
       </c>
       <c r="F78" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G78">
         <v>36</v>
@@ -3050,13 +3050,13 @@
         <v>2</v>
       </c>
       <c r="I78" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J78" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10">
       <c r="A79">
         <v>88</v>
       </c>
@@ -3073,7 +3073,7 @@
         <v>19</v>
       </c>
       <c r="F79" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G79">
         <v>13</v>
@@ -3082,13 +3082,13 @@
         <v>2</v>
       </c>
       <c r="I79" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J79" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10">
       <c r="A80">
         <v>89</v>
       </c>
@@ -3105,22 +3105,22 @@
         <v>23</v>
       </c>
       <c r="F80" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G80">
         <v>25</v>
       </c>
       <c r="H80" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I80" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J80" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10">
       <c r="A81">
         <v>90</v>
       </c>
@@ -3137,22 +3137,22 @@
         <v>36</v>
       </c>
       <c r="F81" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G81">
         <v>17</v>
       </c>
       <c r="H81" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I81" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J81" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10">
       <c r="A82">
         <v>91</v>
       </c>
@@ -3169,7 +3169,7 @@
         <v>43</v>
       </c>
       <c r="F82" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G82">
         <v>1</v>
@@ -3178,18 +3178,18 @@
         <v>2</v>
       </c>
       <c r="I82" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J82" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10">
       <c r="A83">
         <v>92</v>
       </c>
       <c r="B83" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C83" t="s">
         <v>1</v>
@@ -3201,7 +3201,7 @@
         <v>50</v>
       </c>
       <c r="F83" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G83">
         <v>4</v>
@@ -3210,13 +3210,13 @@
         <v>2</v>
       </c>
       <c r="I83" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J83" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10">
       <c r="A84">
         <v>93</v>
       </c>
@@ -3233,7 +3233,7 @@
         <v>42</v>
       </c>
       <c r="F84" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G84">
         <v>22</v>
@@ -3242,18 +3242,18 @@
         <v>2</v>
       </c>
       <c r="I84" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J84" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
       <c r="A85">
         <v>94</v>
       </c>
       <c r="B85" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C85" t="s">
         <v>1</v>
@@ -3265,22 +3265,22 @@
         <v>22</v>
       </c>
       <c r="F85" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G85">
         <v>1</v>
       </c>
       <c r="H85" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I85" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J85" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10">
       <c r="A86">
         <v>95</v>
       </c>
@@ -3297,7 +3297,7 @@
         <v>43</v>
       </c>
       <c r="F86" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G86">
         <v>1</v>
@@ -3306,18 +3306,18 @@
         <v>2</v>
       </c>
       <c r="I86" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J86" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
       <c r="A87">
         <v>96</v>
       </c>
       <c r="B87" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C87" t="s">
         <v>1</v>
@@ -3329,27 +3329,27 @@
         <v>18</v>
       </c>
       <c r="F87" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G87">
         <v>2</v>
       </c>
       <c r="H87" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I87" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J87" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10">
       <c r="A88">
         <v>97</v>
       </c>
       <c r="B88" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C88" t="s">
         <v>1</v>
@@ -3361,7 +3361,7 @@
         <v>61</v>
       </c>
       <c r="F88" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G88">
         <v>4</v>
@@ -3370,18 +3370,18 @@
         <v>2</v>
       </c>
       <c r="I88" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J88" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10">
       <c r="A89">
         <v>98</v>
       </c>
       <c r="B89" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C89" t="s">
         <v>1</v>
@@ -3393,27 +3393,27 @@
         <v>48</v>
       </c>
       <c r="F89" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G89">
         <v>10</v>
       </c>
       <c r="H89" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I89" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J89" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10">
       <c r="A90">
         <v>99</v>
       </c>
       <c r="B90" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C90" t="s">
         <v>2</v>
@@ -3425,7 +3425,7 @@
         <v>35</v>
       </c>
       <c r="F90" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G90">
         <v>12</v>
@@ -3434,18 +3434,18 @@
         <v>2</v>
       </c>
       <c r="I90" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J90" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10">
       <c r="A91">
         <v>100</v>
       </c>
       <c r="B91" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C91" t="s">
         <v>1</v>
@@ -3457,27 +3457,27 @@
         <v>35</v>
       </c>
       <c r="F91" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G91">
         <v>8</v>
       </c>
       <c r="H91" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I91" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J91" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10">
       <c r="A92">
         <v>101</v>
       </c>
       <c r="B92" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C92" t="s">
         <v>1</v>
@@ -3489,7 +3489,7 @@
         <v>40</v>
       </c>
       <c r="F92" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G92">
         <v>12</v>
@@ -3498,18 +3498,18 @@
         <v>2</v>
       </c>
       <c r="I92" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J92" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10">
       <c r="A93">
         <v>102</v>
       </c>
       <c r="B93" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C93" t="s">
         <v>1</v>
@@ -3521,7 +3521,7 @@
         <v>50</v>
       </c>
       <c r="F93" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G93">
         <v>10</v>
@@ -3530,18 +3530,18 @@
         <v>2</v>
       </c>
       <c r="I93" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J93" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10">
       <c r="A94">
         <v>103</v>
       </c>
       <c r="B94" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C94" t="s">
         <v>2</v>
@@ -3553,22 +3553,22 @@
         <v>22</v>
       </c>
       <c r="F94" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G94">
         <v>48</v>
       </c>
       <c r="H94" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I94" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J94" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10">
       <c r="A95">
         <v>104</v>
       </c>
@@ -3585,27 +3585,27 @@
         <v>28</v>
       </c>
       <c r="F95" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G95">
         <v>13</v>
       </c>
       <c r="H95" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I95" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J95" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10">
       <c r="A96">
         <v>105</v>
       </c>
       <c r="B96" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C96" t="s">
         <v>1</v>
@@ -3617,7 +3617,7 @@
         <v>46</v>
       </c>
       <c r="F96" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G96">
         <v>2</v>
@@ -3626,13 +3626,13 @@
         <v>2</v>
       </c>
       <c r="I96" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J96" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10">
       <c r="A97">
         <v>106</v>
       </c>
@@ -3649,7 +3649,7 @@
         <v>43</v>
       </c>
       <c r="F97" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G97">
         <v>10</v>
@@ -3658,13 +3658,13 @@
         <v>2</v>
       </c>
       <c r="I97" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J97" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10">
       <c r="A98">
         <v>107</v>
       </c>
@@ -3681,22 +3681,22 @@
         <v>56</v>
       </c>
       <c r="F98" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G98">
         <v>1</v>
       </c>
       <c r="H98" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I98" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J98" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10">
       <c r="A99">
         <v>108</v>
       </c>
@@ -3713,22 +3713,22 @@
         <v>30</v>
       </c>
       <c r="F99" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G99">
         <v>37</v>
       </c>
       <c r="H99" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I99" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J99" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10">
       <c r="A100">
         <v>109</v>
       </c>
@@ -3745,7 +3745,7 @@
         <v>53</v>
       </c>
       <c r="F100" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G100">
         <v>10</v>
@@ -3754,18 +3754,18 @@
         <v>2</v>
       </c>
       <c r="I100" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J100" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10">
       <c r="A101">
         <v>110</v>
       </c>
       <c r="B101" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C101" t="s">
         <v>1</v>
@@ -3777,7 +3777,7 @@
         <v>26</v>
       </c>
       <c r="F101" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G101">
         <v>24</v>
@@ -3786,13 +3786,13 @@
         <v>2</v>
       </c>
       <c r="I101" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J101" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10">
       <c r="A102">
         <v>111</v>
       </c>
@@ -3809,27 +3809,27 @@
         <v>39</v>
       </c>
       <c r="F102" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G102">
         <v>21</v>
       </c>
       <c r="H102" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I102" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J102" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10">
       <c r="A103">
         <v>112</v>
       </c>
       <c r="B103" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C103" t="s">
         <v>2</v>
@@ -3841,7 +3841,7 @@
         <v>47</v>
       </c>
       <c r="F103" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G103">
         <v>6</v>
@@ -3850,13 +3850,13 @@
         <v>2</v>
       </c>
       <c r="I103" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J103" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10">
       <c r="A104">
         <v>113</v>
       </c>
@@ -3873,7 +3873,7 @@
         <v>34</v>
       </c>
       <c r="F104" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G104">
         <v>7</v>
@@ -3882,18 +3882,18 @@
         <v>2</v>
       </c>
       <c r="I104" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J104" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10">
       <c r="A105">
         <v>114</v>
       </c>
       <c r="B105" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C105" t="s">
         <v>1</v>
@@ -3905,7 +3905,7 @@
         <v>47</v>
       </c>
       <c r="F105" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G105">
         <v>4</v>
@@ -3914,18 +3914,18 @@
         <v>2</v>
       </c>
       <c r="I105" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J105" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10">
       <c r="A106">
         <v>115</v>
       </c>
       <c r="B106" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C106" t="s">
         <v>1</v>
@@ -3937,7 +3937,7 @@
         <v>58</v>
       </c>
       <c r="F106" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G106">
         <v>11</v>
@@ -3946,18 +3946,18 @@
         <v>2</v>
       </c>
       <c r="I106" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J106" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10">
       <c r="A107">
         <v>116</v>
       </c>
       <c r="B107" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C107" t="s">
         <v>2</v>
@@ -3969,7 +3969,7 @@
         <v>22</v>
       </c>
       <c r="F107" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G107">
         <v>12</v>
@@ -3978,18 +3978,18 @@
         <v>2</v>
       </c>
       <c r="I107" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J107" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10">
       <c r="A108">
         <v>117</v>
       </c>
       <c r="B108" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C108" t="s">
         <v>2</v>
@@ -4001,7 +4001,7 @@
         <v>24</v>
       </c>
       <c r="F108" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G108">
         <v>9</v>
@@ -4010,18 +4010,18 @@
         <v>2</v>
       </c>
       <c r="I108" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J108" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10">
       <c r="A109">
         <v>118</v>
       </c>
       <c r="B109" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C109" t="s">
         <v>2</v>
@@ -4033,7 +4033,7 @@
         <v>24</v>
       </c>
       <c r="F109" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G109">
         <v>22</v>
@@ -4042,13 +4042,13 @@
         <v>2</v>
       </c>
       <c r="I109" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J109" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10">
       <c r="A110">
         <v>119</v>
       </c>
@@ -4065,7 +4065,7 @@
         <v>56</v>
       </c>
       <c r="F110" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G110">
         <v>3</v>
@@ -4074,13 +4074,13 @@
         <v>2</v>
       </c>
       <c r="I110" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J110" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10">
       <c r="A111">
         <v>120</v>
       </c>
@@ -4097,7 +4097,7 @@
         <v>29</v>
       </c>
       <c r="F111" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G111">
         <v>3</v>
@@ -4106,18 +4106,18 @@
         <v>2</v>
       </c>
       <c r="I111" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J111" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10">
       <c r="A112">
         <v>121</v>
       </c>
       <c r="B112" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C112" t="s">
         <v>1</v>
@@ -4129,7 +4129,7 @@
         <v>52</v>
       </c>
       <c r="F112" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G112">
         <v>13</v>
@@ -4138,18 +4138,18 @@
         <v>2</v>
       </c>
       <c r="I112" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J112" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10">
       <c r="A113">
         <v>122</v>
       </c>
       <c r="B113" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C113" t="s">
         <v>2</v>
@@ -4161,7 +4161,7 @@
         <v>28</v>
       </c>
       <c r="F113" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G113">
         <v>6</v>
@@ -4170,18 +4170,18 @@
         <v>2</v>
       </c>
       <c r="I113" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J113" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10">
       <c r="A114">
         <v>123</v>
       </c>
       <c r="B114" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C114" t="s">
         <v>1</v>
@@ -4193,7 +4193,7 @@
         <v>51</v>
       </c>
       <c r="F114" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G114">
         <v>17</v>
@@ -4202,18 +4202,18 @@
         <v>2</v>
       </c>
       <c r="I114" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J114" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10">
       <c r="A115">
         <v>124</v>
       </c>
       <c r="B115" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C115" t="s">
         <v>1</v>
@@ -4225,27 +4225,27 @@
         <v>31</v>
       </c>
       <c r="F115" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G115">
         <v>1</v>
       </c>
       <c r="H115" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I115" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J115" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10">
       <c r="A116">
         <v>126</v>
       </c>
       <c r="B116" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C116" t="s">
         <v>2</v>
@@ -4257,7 +4257,7 @@
         <v>53</v>
       </c>
       <c r="F116" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G116">
         <v>10</v>
@@ -4266,18 +4266,18 @@
         <v>2</v>
       </c>
       <c r="I116" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J116" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10">
       <c r="A117">
         <v>127</v>
       </c>
       <c r="B117" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C117" t="s">
         <v>2</v>
@@ -4289,7 +4289,7 @@
         <v>20</v>
       </c>
       <c r="F117" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G117">
         <v>10</v>
@@ -4298,18 +4298,18 @@
         <v>2</v>
       </c>
       <c r="I117" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J117" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10">
       <c r="A118">
         <v>128</v>
       </c>
       <c r="B118" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C118" t="s">
         <v>2</v>
@@ -4321,7 +4321,7 @@
         <v>19</v>
       </c>
       <c r="F118" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G118">
         <v>10</v>
@@ -4330,18 +4330,18 @@
         <v>2</v>
       </c>
       <c r="I118" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J118" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10">
       <c r="A119">
         <v>129</v>
       </c>
       <c r="B119" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C119" t="s">
         <v>2</v>
@@ -4353,7 +4353,7 @@
         <v>43</v>
       </c>
       <c r="F119" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G119">
         <v>21</v>
@@ -4362,18 +4362,18 @@
         <v>2</v>
       </c>
       <c r="I119" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J119" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10">
       <c r="A120">
         <v>130</v>
       </c>
       <c r="B120" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C120" t="s">
         <v>1</v>
@@ -4385,7 +4385,7 @@
         <v>45</v>
       </c>
       <c r="F120" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G120">
         <v>5</v>
@@ -4394,10 +4394,10 @@
         <v>2</v>
       </c>
       <c r="I120" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J120" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
